--- a/research/GemBreak_Influencer_Lists.xlsx
+++ b/research/GemBreak_Influencer_Lists.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Jaspy's Case Breaks</t>
+          <t>mysterymilo007</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>mid ESTIMATE</t>
+          <t>73k IG (2026-07-18 snippet)</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -747,47 +747,47 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>IG @jaspyscasebreaks ; site jaspyscasebreaks.com ; Whatnot/Fanatics/eBay</t>
+          <t>Instagram https://www.instagram.com/mysterymilo007/</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://jaspyscasebreaks.com</t>
+          <t>none (also Snap @mysterymilo, TikTok)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; REACHABLE: public business email</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Backyard Breaks</t>
+          <t>ChrisG</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -819,57 +819,57 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>macro ESTIMATE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>Whatnot https://whatnot.com/user/backyardbreaks (4.8*, 28k reviews) ; site backyardbreaks.com ; IG @backyardbreaks</t>
+          <t>YouTube https://www.youtube.com/watch?v=MD6zLZVgLeY</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>https://backyardbreaks.com</t>
+          <t>tiltedtwinz@pm.me (public email)</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); macro reach (higher cost); reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; REACHABLE: public business email</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -881,17 +881,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Sports Box Breaks (SBB)</t>
+          <t>OneEyedGregg</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -901,57 +901,57 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>mid ESTIMATE</t>
+          <t>Kick ~14.9k (snippet)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>IG (Sports Box Breaks)</t>
+          <t>Kick https://kick.com/oneeyedgregg ; YouTube https://www.youtube.com/@Oneeyedgregg ; Twitch https://www.twitch.tv/oneeyedgregg ; X https://x.com/oneeyedgregg</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (oeg.gg hub)</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -963,17 +963,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Blez</t>
+          <t>lacedupny (Laced Up Worldwide)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -983,57 +983,57 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>mid ESTIMATE</t>
+          <t>~20k IG ESTIMATE (pikdo mirror 2026-07-18)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Whatnot https://whatnot.com/user/blez (4.9*, 1.3k reviews)</t>
+          <t>Instagram https://www.instagram.com/lacedupny/</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>retail store (multi-location)</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1045,17 +1045,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>rogerrips</t>
+          <t>Rydurz</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>~190.7k TT / 76.2k IG / 27.2k Whatnot</t>
+          <t>Kick ~24.2k (Sept-2025 snippet)</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://tiktok.com/@rogerrips (190.7k) ; IG https://instagram.com/rogerrips (76.2k) ; Whatnot https://whatnot.com/user/rogerrips (27.2k) ; site rogerrips.com</t>
+          <t>Kick https://kick.com/rydurz ; X https://x.com/rydurz</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://rogerrips.com</t>
+          <t>none (coderydurz.com hub)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Randolph (Randolph Pokemon)</t>
+          <t>Jules (Julsy)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>~671k YT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1157,22 +1157,22 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://youtube.com/@RandolphPokemon (671k) ; store pokerand.net</t>
+          <t>YouTube https://www.youtube.com/channel/UCrUFQtoCMdDZ06whZQodFuA ; X https://x.com/JulsyCS ; Kick https://kick.com/JULSY</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>https://pokerand.net</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1209,17 +1209,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Cardlines Breaks</t>
+          <t>RobZn</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1229,32 +1229,32 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>mid ESTIMATE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>eBay + IG (Cardlines)</t>
+          <t>Kick https://kick.com/robznnncs</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://cardlines.com</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1264,22 +1264,22 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Neel Alwani (NeelTPT)</t>
+          <t>@the_happy_budget</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>watch</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>~187k IG</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/neeltpt ; YouTube https://youtube.com/channel/UCDE-NiU6Nby5XqwM-gYHfCA ; TikTok https://tiktok.com/@neeltpt</t>
+          <t>https://www.tiktok.com/@the_happy_budget</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>neeleshalwani@hotmail.com ; neelesh@timepiecetradingllc.com</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1346,22 +1346,22 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>watch/collectible audience; REACHABLE: public business email</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Gio The Pokemon Puller</t>
+          <t>@winonakicks</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>~11k IG</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/pokemonpuller (11k)</t>
+          <t>https://www.tiktok.com/@winonakicks</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>mysterymilo007</t>
+          <t>mysterypacks.de</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1475,27 +1475,27 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>73k IG (2026-07-18 snippet)</t>
+          <t>52.1k TikTok (2026-07-18)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/mysterymilo007/</t>
+          <t>TikTok https://www.tiktok.com/@mysterypacks.de</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>none (also Snap @mysterymilo, TikTok)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; REACHABLE: public business email</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ChrisG</t>
+          <t>Svensk Drama</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~67.8k SUBS (2026-06-24, single-source)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/watch?v=MD6zLZVgLeY</t>
+          <t>YouTube https://www.youtube.com/@SvenskDrama</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>tiltedtwinz@pm.me (public email)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; REACHABLE: public business email</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Joshua Mills</t>
+          <t>unboxdisneypinco</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>~34.6k IG</t>
+          <t>2,751 IG (2026-07-18)</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>IG (Joshua Mills)</t>
+          <t>Instagram https://www.instagram.com/unboxdisneypinco/</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>business email available</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1669,27 +1669,27 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; REACHABLE: public business email</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>pm7_john</t>
+          <t>CrimsonYT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>~40k IG</t>
+          <t>~5k YT SUBS (SERP)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/pm7_john</t>
+          <t>YouTube https://www.youtube.com/channel/UCI2grI-9aZh9kyuPxWAFvxg ; X https://x.com/CrimsonYT101</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>business email listed in IG bio</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; REACHABLE: public business email</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1783,37 +1783,37 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Deep Pocket Monster</t>
+          <t>clvkingbets</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>~1.6M YT</t>
+          <t>~18.8k</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://youtube.com/c/DeepPocketMonster (~1.6M) ; IG @deeppocketmonsterofficial</t>
+          <t>TikTok @clvkingbets (18.8k)</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1865,37 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>RealBreakingNate</t>
+          <t>gurusportsbetting</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>~2M YT</t>
+          <t>~19.3k</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://youtube.com/@RealBreakingNate (2M)</t>
+          <t>TikTok @gurusportsbetting (19.3k)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1947,37 +1947,37 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Leonhart</t>
+          <t>lucyburdge1</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>~2M YT</t>
+          <t>~19.5k</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://youtube.com/@Leonhart (2M)</t>
+          <t>TikTok @lucyburdge1 (19.5k)</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1987,17 +1987,17 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2029,37 +2029,37 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>UnlistedLeaf</t>
+          <t>brucie.sports</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>~2.7M YT</t>
+          <t>~23.9k</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://youtube.com/@UnlistedLeaf (2.7M) ; IG @unlistedleaf (110k)</t>
+          <t>TikTok @brucie.sports (23.9k)</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2111,37 +2111,37 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>PokeRev</t>
+          <t>codycoverspreads</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>~3.3M YT</t>
+          <t>~27.2k</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://youtube.com/@PokeRev (3.3M)</t>
+          <t>TikTok @codycoverspreads (27.2k)</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>collectible BREAKER/opener - GemBreak's core format; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Roman Sharf (Luxury Bazaar)</t>
+          <t>SweetFlips (group)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>watch</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2213,32 +2213,32 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>macro ESTIMATE</t>
+          <t>~32k Kick</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>YouTube (Luxury Bazaar)</t>
+          <t>Kick @SweetFlips (Dennylo, Damil, Jacko, Pingue, Baka, Motion, Blendz)</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>https://luxurybazaar.com</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -2248,22 +2248,22 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>watch/collectible audience; macro reach (higher cost); reachable via site/store</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>OneEyedGregg</t>
+          <t>Aiden Gambles</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>micro-mid</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -2295,27 +2295,27 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Kick ~14.9k (snippet)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Kick https://kick.com/oneeyedgregg ; YouTube https://www.youtube.com/@Oneeyedgregg ; Twitch https://www.twitch.tv/oneeyedgregg ; X https://x.com/oneeyedgregg</t>
+          <t>YouTube https://www.youtube.com/@AidenGambles ; X https://x.com/aiden_gambles</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>none (oeg.gg hub)</t>
+          <t>none (Discord community)</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -2335,17 +2335,17 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>lacedupny (Laced Up Worldwide)</t>
+          <t>Bouchonnoir</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>micro-mid</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2377,27 +2377,27 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>~20k IG ESTIMATE (pikdo mirror 2026-07-18)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/lacedupny/</t>
+          <t>YouTube https://www.youtube.com/@Bouchonnoir</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>retail store (multi-location)</t>
+          <t>none (bouchonnoir.gg hub)</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Rydurz</t>
+          <t>GW1917</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>micro-mid</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -2459,27 +2459,27 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Kick ~24.2k (Sept-2025 snippet)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Kick https://kick.com/rydurz ; X https://x.com/rydurz</t>
+          <t>YouTube https://www.youtube.com/@GW1917gaming</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>none (coderydurz.com hub)</t>
+          <t>none (gw1917gaming.com)</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Jules (Julsy)</t>
+          <t>Sloth (SlothCSGO)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>micro-mid</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/channel/UCrUFQtoCMdDZ06whZQodFuA ; X https://x.com/JulsyCS ; Kick https://kick.com/JULSY</t>
+          <t>YouTube https://www.youtube.com/@SlothCSGO ; X https://x.com/slothhcsgo</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (slothrewards.com hub)</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>RobZn</t>
+          <t>TylerPlaysLive</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>micro-mid</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Kick https://kick.com/robznnncs</t>
+          <t>YouTube https://www.youtube.com/@tylerplayslive26 ; TikTok https://www.tiktok.com/@tylerplaylive ; X https://x.com/tylerplayslive ; Kick https://kick.com/tylerplayslive</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (BlissBox LLC FB page)</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>@the_happy_budget</t>
+          <t>emilyyyrosess</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_happy_budget</t>
+          <t>Instagram https://www.instagram.com/emilyyyrosess/</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>@winonakicks</t>
+          <t>golddigger_5</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@winonakicks</t>
+          <t>TikTok https://www.tiktok.com/@golddigger_5</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>mysterypacks.de</t>
+          <t>hypedropcrazybattles</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>52.1k TikTok (2026-07-18)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@mysterypacks.de</t>
+          <t>TikTok https://www.tiktok.com/@hypedropcrazybattles</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Svensk Drama</t>
+          <t>Sebknowsbest</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>~67.8k SUBS (2026-06-24, single-source)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@SvenskDrama</t>
+          <t>TikTok https://www.tiktok.com/@sebknowsbest</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Sports Card Investor (Geoff Wilson)</t>
+          <t>tshockz22</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -3033,27 +3033,27 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>~213k IG</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/sportscardinvestor (213k) ; site sportscardinvestor.com</t>
+          <t>TikTok https://www.tiktok.com/@tshockz22</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>https://sportscardinvestor.com</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -3063,27 +3063,27 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Gary 'King Pokemon'</t>
+          <t>Brian Christopher (BCSlots)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>~49.3k IG</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>IG (King Pokemon)</t>
+          <t>YouTube @BrianChristopherSlots ; site bcslots.com</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -3135,37 +3135,37 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); reachable via site/store</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$6,000-30,000</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$90,000-700,000+</t>
         </is>
       </c>
     </row>
@@ -3177,17 +3177,17 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Twin Toys Fam</t>
+          <t>LetsGiveItASpin (Kim Hultman)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -3197,32 +3197,32 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>~52.3k IG</t>
+          <t>mid-macro</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/twintoysfam (52.3k)</t>
+          <t>YouTube @LetsGiveItASpin</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -3259,17 +3259,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>unboxdisneypinco</t>
+          <t>CasinoGrounds</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>2,751 IG (2026-07-18)</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/unboxdisneypinco/</t>
+          <t>YouTube (CasinoGrounds)</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -3299,37 +3299,37 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>$50-300</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>$450-4,400</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CrimsonYT</t>
+          <t>Play NJ Slot Guy</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>~5k YT SUBS (SERP)</t>
+          <t>micro-mid</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/channel/UCI2grI-9aZh9kyuPxWAFvxg ; X https://x.com/CrimsonYT101</t>
+          <t>YouTube (Play NJ Slot Guy)</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -3381,27 +3381,27 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -3423,17 +3423,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Aiden Gambles</t>
+          <t>Fruity Slots (Josh/Jamie/Scottie)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -3453,37 +3453,37 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@AidenGambles ; X https://x.com/aiden_gambles</t>
+          <t>YouTube @FruitySlots</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>none (Discord community)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -3505,17 +3505,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Bouchonnoir</t>
+          <t>BenderWins Sports Betting</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -3525,57 +3525,57 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>micro ESTIMATE</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@Bouchonnoir</t>
+          <t>TikTok @BenderWinsSportsBetting</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>none (bouchonnoir.gg hub)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>GW1917</t>
+          <t>weberbets</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -3607,57 +3607,57 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~40.4k</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@GW1917gaming</t>
+          <t>TikTok @weberbets (40.4k)</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>none (gw1917gaming.com)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3669,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Sloth (SlothCSGO)</t>
+          <t>takingthepoints</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3689,57 +3689,57 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~60.4k</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@SlothCSGO ; X https://x.com/slothhcsgo</t>
+          <t>TikTok @takingthepoints (60.4k)</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>none (slothrewards.com hub)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>TylerPlaysLive</t>
+          <t>jommypogs</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -3771,57 +3771,57 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~61.4k TT</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@tylerplayslive26 ; TikTok https://www.tiktok.com/@tylerplaylive ; X https://x.com/tylerplayslive ; Kick https://kick.com/tylerplayslive</t>
+          <t>TikTok @jommypogs</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>none (BlissBox LLC FB page)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -3833,17 +3833,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>emilyyyrosess</t>
+          <t>jstros_</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~62.1k TT</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/emilyyyrosess/</t>
+          <t>TikTok @jstros_</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -3873,27 +3873,27 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3915,17 +3915,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>golddigger_5</t>
+          <t>binkyloveslots</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~62.1k TT</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@golddigger_5</t>
+          <t>TikTok @binkyloveslots</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -3955,27 +3955,27 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -3997,17 +3997,17 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>hypedropcrazybattles</t>
+          <t>ahmed_elpoker</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~62.3k TT</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@hypedropcrazybattles</t>
+          <t>TikTok @ahmed_elpoker</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -4037,27 +4037,27 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -4079,17 +4079,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Sebknowsbest</t>
+          <t>thadrunkgambler</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~64k TT</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@sebknowsbest</t>
+          <t>TikTok @thadrunkgambler</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -4119,27 +4119,27 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>tshockz22</t>
+          <t>thequeenofmedia</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~79.8k TT</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@tshockz22</t>
+          <t>TikTok @thequeenofmedia</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -4201,27 +4201,27 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>lito_gmbl</t>
+          <t>erinkatedolan</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>~163.3k TikTok ESTIMATE (~2023)</t>
+          <t>~81.3k</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@lito_gmbl ; X https://twitter.com/lito_gmbl</t>
+          <t>TikTok @erinkatedolan (81.3k)</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -4325,17 +4325,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Classybeef</t>
+          <t>casino_memes</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>~194k Kick ESTIMATE</t>
+          <t>~2k IG</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>https://kick.com/classybeef</t>
+          <t>IG https://instagram.com/casino_memes</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -4365,37 +4365,37 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Cheesur</t>
+          <t>EataHoagie</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -4427,17 +4427,17 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>~203k Kick ESTIMATE</t>
+          <t>~3.6k X</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>https://kick.com/cheesur</t>
+          <t>X @EataHoagie</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -4447,37 +4447,37 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -4489,17 +4489,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>PimpCSGO (Jacob Winneche)</t>
+          <t>hideousslots</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>~250k SUBS ESTIMATE</t>
+          <t>~3.9k X</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@PIMP</t>
+          <t>X @hideousslots</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -4529,37 +4529,37 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -4571,17 +4571,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>ProdigyDDK</t>
+          <t>abbypoker_</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -4591,57 +4591,57 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>~251-270k SUBS ESTIMATE (2026)</t>
+          <t>~5.3k X</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@prodigyddk ; Instagram https://www.instagram.com/prodigy.ddk/ ; Twitch https://twitch.tv/prodigyddk</t>
+          <t>X @abbypoker_</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>none (site prodigyddk.com)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O49" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Dima_wallhacks</t>
+          <t>lito_gmbl</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4673,17 +4673,17 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>~406k SUBS ESTIMATE</t>
+          <t>~163.3k TikTok ESTIMATE (~2023)</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Dima_wallhacks</t>
+          <t>TikTok https://www.tiktok.com/@lito_gmbl ; X https://twitter.com/lito_gmbl</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Moses the Jeweler</t>
+          <t>Classybeef</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>prediction-market</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~194k Kick ESTIMATE</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>X https://x.com/mosesjewelry</t>
+          <t>https://kick.com/classybeef</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -4775,37 +4775,37 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>3.575</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>cardcollector2 (Ryan Johnson)</t>
+          <t>Cheesur</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -4837,17 +4837,17 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>~176k IG</t>
+          <t>~203k Kick ESTIMATE</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/cardcollector2 (176k)</t>
+          <t>https://kick.com/cheesur</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Maherco</t>
+          <t>PimpCSGO (Jacob Winneche)</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -4919,17 +4919,17 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~250k SUBS ESTIMATE</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>https://kick.com/maherco</t>
+          <t>https://www.youtube.com/@PIMP</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -4959,17 +4959,17 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Renyan</t>
+          <t>ProdigyDDK</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -5001,27 +5001,27 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~251-270k SUBS ESTIMATE (2026)</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>https://www.twitch.tv/renyan</t>
+          <t>YouTube https://www.youtube.com/@prodigyddk ; Instagram https://www.instagram.com/prodigy.ddk/ ; Twitch https://twitch.tv/prodigyddk</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (site prodigyddk.com)</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -5041,17 +5041,17 @@
       </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Curly (The Curly Fella)</t>
+          <t>Dima_wallhacks</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -5083,17 +5083,17 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~406k SUBS ESTIMATE</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thecurlyfella</t>
+          <t>https://www.youtube.com/@Dima_wallhacks</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -5123,17 +5123,17 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O55" s="6" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>@culturekicks</t>
+          <t>Maherco</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@culturekicks</t>
+          <t>https://kick.com/maherco</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>@soleloco</t>
+          <t>Renyan</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soleloco</t>
+          <t>https://www.twitch.tv/renyan</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>@air.jumps.official</t>
+          <t>Curly (The Curly Fella)</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@air.jumps.official</t>
+          <t>https://www.tiktok.com/@thecurlyfella</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>@ioannalaou</t>
+          <t>@culturekicks</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ioannalaou</t>
+          <t>https://www.tiktok.com/@culturekicks</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>csgo.gambling</t>
+          <t>@soleloco</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@csgo.gambling</t>
+          <t>https://www.tiktok.com/@soleloco</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>dizzydankss (DizzyDanks24)</t>
+          <t>@air.jumps.official</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@dizzydankss</t>
+          <t>https://www.tiktok.com/@air.jumps.official</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>hypedropbalotelli</t>
+          <t>@ioannalaou</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@hypedropbalotelli</t>
+          <t>https://www.tiktok.com/@ioannalaou</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>kelvinmboik</t>
+          <t>csgo.gambling</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@kelvinmboik</t>
+          <t>TikTok https://www.tiktok.com/@csgo.gambling</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>laceduphollywood</t>
+          <t>dizzydankss (DizzyDanks24)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -5826,22 +5826,22 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/laceduphollywood/</t>
+          <t>TikTok https://www.tiktok.com/@dizzydankss</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>retail store</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>OnlyCrunchy</t>
+          <t>hypedropbalotelli</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>X https://x.com/onlycrunchy</t>
+          <t>TikTok https://www.tiktok.com/@hypedropbalotelli</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>pizza_god1 (Kody Garrett)</t>
+          <t>kelvinmboik</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@pizza_god1</t>
+          <t>TikTok https://www.tiktok.com/@kelvinmboik</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>quickhypedrop</t>
+          <t>laceduphollywood</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@quickhypedrop</t>
+          <t>Instagram https://www.instagram.com/laceduphollywood/</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>retail store</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>rillabox.openings</t>
+          <t>OnlyCrunchy</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@rillabox.openings</t>
+          <t>X https://x.com/onlycrunchy</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="N68" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>twitch.tvkushti_ (kushti_)</t>
+          <t>pizza_god1 (Kody Garrett)</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/twitch.tvkushti_/</t>
+          <t>TikTok https://www.tiktok.com/@pizza_god1</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>@harrisonevel</t>
+          <t>quickhypedrop</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -6318,10 +6318,14 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr"/>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>TikTok https://www.tiktok.com/@quickhypedrop</t>
+        </is>
+      </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
           <t>none</t>
@@ -6329,7 +6333,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -6349,7 +6353,7 @@
       </c>
       <c r="N70" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O70" s="4" t="inlineStr">
@@ -6371,7 +6375,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>@yankeekicks</t>
+          <t>rillabox.openings</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -6396,10 +6400,14 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Instagram/YouTube</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>TikTok https://www.tiktok.com/@rillabox.openings</t>
+        </is>
+      </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
           <t>none</t>
@@ -6407,7 +6415,7 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
@@ -6427,7 +6435,7 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
@@ -6449,7 +6457,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>ArrowCS</t>
+          <t>twitch.tvkushti_ (kushti_)</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -6474,10 +6482,14 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Instagram https://www.instagram.com/twitch.tvkushti_/</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
           <t>none</t>
@@ -6485,7 +6497,7 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -6505,7 +6517,7 @@
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
@@ -6527,7 +6539,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Devon Gard</t>
+          <t>@harrisonevel</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -6552,7 +6564,7 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>YouTube/LinkedIn</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr"/>
@@ -6563,7 +6575,7 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -6583,7 +6595,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr">
@@ -6605,7 +6617,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>megalodon888</t>
+          <t>@yankeekicks</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -6630,7 +6642,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Twitch/Kick</t>
+          <t>Instagram/YouTube</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr"/>
@@ -6641,7 +6653,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -6661,7 +6673,7 @@
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
@@ -6683,7 +6695,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>HaiX</t>
+          <t>ArrowCS</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -6693,7 +6705,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -6703,19 +6715,15 @@
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>~526k SUBS ESTIMATE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@HaiX</t>
-        </is>
-      </c>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr"/>
       <c r="I75" s="6" t="inlineStr">
         <is>
           <t>none</t>
@@ -6723,7 +6731,7 @@
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -6743,17 +6751,17 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6773,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>FURI</t>
+          <t>Devon Gard</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -6775,7 +6783,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -6785,19 +6793,15 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>~535k SUBS ESTIMATE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@FURI</t>
-        </is>
-      </c>
+          <t>YouTube/LinkedIn</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
           <t>none</t>
@@ -6805,7 +6809,7 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -6825,17 +6829,17 @@
       </c>
       <c r="N76" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6851,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>neokCS</t>
+          <t>megalodon888</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -6857,7 +6861,7 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -6867,19 +6871,15 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>~553k SUBS ESTIMATE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@neokCS</t>
-        </is>
-      </c>
+          <t>Twitch/Kick</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr">
         <is>
           <t>none</t>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
@@ -6907,17 +6907,17 @@
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
     </row>
@@ -6929,17 +6929,17 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>WatchGamesTV</t>
+          <t>Raja Richter (The Big Jackpot)</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>~535-559k SUBS ESTIMATE (2026)</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -6959,37 +6959,37 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@watchgamestv ; X https://twitter.com/watchgamestv</t>
+          <t>YouTube @TheBigJackpot ; IG @thebigjackpot</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>linktr.ee/watchgamestv</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
@@ -7011,37 +7011,37 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Orangie</t>
+          <t>Lady Luck HQ</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>N/A (crowded namespace)</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Twitch https://www.twitch.tv/orangieyt ; Kick https://kick.com/orangie ; X https://x.com/orangie ; YouTube https://www.youtube.com/watch?v=o2pvnwCtc0U</t>
+          <t>YouTube @LadyLuckHQ</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -7051,27 +7051,27 @@
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr">
@@ -7093,17 +7093,17 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>tani.chuu</t>
+          <t>NG Slot</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -7113,17 +7113,17 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>~13.5k IG</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/tani.chuu</t>
+          <t>YouTube @NGSlot</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -7148,22 +7148,22 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$6,000-30,000</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$90,000-700,000+</t>
         </is>
       </c>
     </row>
@@ -7175,17 +7175,17 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>crezzelia</t>
+          <t>Mr. Hand Pay</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -7195,17 +7195,17 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>~16.6k IG / 15k TT</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>IG @crezzelia ; TikTok @crezzelia</t>
+          <t>YouTube @MrHandPay</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -7230,22 +7230,22 @@
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$6,000-30,000</t>
         </is>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$90,000-700,000+</t>
         </is>
       </c>
     </row>
@@ -7257,17 +7257,17 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>mister_fuji_</t>
+          <t>Pompsie Slots</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -7277,17 +7277,17 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>~22.1k IG</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/mister_fuji_</t>
+          <t>YouTube (Pompsie)</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -7317,17 +7317,17 @@
       </c>
       <c r="N82" s="5" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7339,17 +7339,17 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>coops_collection (Coop)</t>
+          <t>PokerMetarb</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -7359,17 +7359,17 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>micro ESTIMATE</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/coops_collection</t>
+          <t>YouTube (PokerMetarb)</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -7399,17 +7399,17 @@
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7421,17 +7421,17 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>pokenomics_</t>
+          <t>CasinoDaddy</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -7441,17 +7441,17 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>micro-mid ESTIMATE</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/pokenomics_</t>
+          <t>Twitch https://twitch.tv/casinodaddy</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -7476,22 +7476,22 @@
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$6,000-30,000</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$90,000-700,000+</t>
         </is>
       </c>
     </row>
@@ -7503,17 +7503,17 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>tradenatural</t>
+          <t>Taour (Noamane Boukhari)</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>micro-mid ESTIMATE</t>
+          <t>mid-macro</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/tradenatural</t>
+          <t>Kick (Taour)</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -7563,17 +7563,17 @@
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O85" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7585,17 +7585,17 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>cardcollector.co.uk</t>
+          <t>Tiagovski</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>micro ESTIMATE</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/cardcollector.co.uk</t>
+          <t>Kick/Twitch @Tiagovski555</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="N86" s="5" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7667,17 +7667,17 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>elitesportscardsandmem</t>
+          <t>teufeurs</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -7687,17 +7687,17 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>micro ESTIMATE</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/elitesportscardsandmem</t>
+          <t>Twitch @teufeurs</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O87" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7749,17 +7749,17 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>jtsportscardsandcollectables</t>
+          <t>YoutubeVLR</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>sports-cards</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -7769,17 +7769,17 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>micro ESTIMATE</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/jtsportscardsandcollectables</t>
+          <t>YouTube (VLR)</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -7809,17 +7809,17 @@
       </c>
       <c r="N88" s="5" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7831,17 +7831,17 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>PokiChloe</t>
+          <t>All Casino Action</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>~60k+ YT</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://youtube.com/@PokiChloe (~60k)</t>
+          <t>YouTube (All Casino Action)</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7913,17 +7913,17 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>austinjohnplays</t>
+          <t>Chipmonkz Slots</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -7933,17 +7933,17 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>~63.7k IG</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/austinjohnplays</t>
+          <t>YouTube (Chipmonkz)</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -7953,12 +7953,12 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="N90" s="5" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7995,17 +7995,17 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Officiallywhelmed</t>
+          <t>Toaster (Toaster Gambles)</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -8015,17 +8015,17 @@
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>~98k TT</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>TikTok @officiallywhelmed</t>
+          <t>YouTube/Kick (Toaster)</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; engaged micro/nano - GemBreak sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O91" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Amsterdam Vintage Watches</t>
+          <t>Cabrzy</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>watch-vintage</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -8097,47 +8097,47 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>~192k IG</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/amsterdamvintagewatches (192k) ; site amsterdamvintagewatches.com</t>
+          <t>YouTube/Kick (Cabrzy)</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>https://amsterdamvintagewatches.com</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="M92" s="4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="N92" s="5" t="inlineStr">
         <is>
-          <t>gambling-native audience (comfortable with the mechanic); reachable via site/store</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>JuicyCSGO</t>
+          <t>TactPlaysGames</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>~529k SUBS ESTIMATE (2026)</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/channel/UC_i5slkwxbZKPeh9x2QWkSw ; X https://x.com/juicycsg</t>
+          <t>YouTube (Tact)</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -8199,37 +8199,37 @@
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O93" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8241,37 +8241,37 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>TimTheTatman</t>
+          <t>The Bandit (NightRush/Slot Video)</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>macro (multi-M)</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Kick/YouTube</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>https://kick.com/timthetatman</t>
+          <t>YouTube (The Bandit)</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -8281,37 +8281,37 @@
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8323,37 +8323,37 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Nadeshot</t>
+          <t>AyeZee</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>macro (multi-M)</t>
+          <t>mid-macro</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>YouTube/Twitch</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>https://www.twitch.tv/nadeshot</t>
+          <t>Kick/YouTube @AyeZee</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
@@ -8363,37 +8363,37 @@
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O95" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8405,37 +8405,37 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Trainwreckstv</t>
+          <t>GambleDude</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>macro (multi-M)</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>https://kick.com/trainwreckstv</t>
+          <t>YouTube (GambleDude)</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -8445,37 +8445,37 @@
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N96" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8487,37 +8487,37 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Xposed</t>
+          <t>The Juice Betting</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>N/A (macro reputation)</t>
+          <t>mid ESTIMATE</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Kick https://kick.com/xposed ; YouTube https://www.youtube.com/channel/UC0U5sBczEr2ASp4T6hSLvag</t>
+          <t>TikTok @TheJuiceBetting</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -8527,37 +8527,37 @@
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O97" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8569,37 +8569,37 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Steve Will Do It</t>
+          <t>MattyBetss</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>macro &gt;&gt;1M</t>
+          <t>~100k+</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>X/Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>https://x.com/stevewilldoit</t>
+          <t>TikTok @MattyBetss (100k+)</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -8609,37 +8609,37 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N98" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8651,37 +8651,37 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Paul Cuffaro</t>
+          <t>jbigsdfs</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>macro (likely &gt;1M)</t>
+          <t>~106.4k</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKFtfFitaK83yBc0rlg9m1A</t>
+          <t>TikTok @jbigsdfs (106.4k)</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -8691,37 +8691,37 @@
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O99" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P99" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8733,37 +8733,37 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Anomaly</t>
+          <t>gamblers.gambling</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>~3.3M</t>
+          <t>~154k IG</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Anomaly</t>
+          <t>IG https://instagram.com/gamblers.gambling (154k)</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -8773,37 +8773,37 @@
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N100" s="5" t="inlineStr">
         <is>
-          <t>live case/box unbox - same break mechanic as GemBreak; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Pokezenn</t>
+          <t>Classybeef (group)</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>pokemon-collectible</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -8835,17 +8835,17 @@
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>~278k TT</t>
+          <t>~194k</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://tiktok.com/@pokezenn</t>
+          <t>Kick https://kick.com/classybeef (Georgi, Jonte, Biggo, Freddy, Max, Rune)</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>collectible-card audience fit; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O101" s="6" t="inlineStr">

--- a/research/GemBreak_Influencer_Lists.xlsx
+++ b/research/GemBreak_Influencer_Lists.xlsx
@@ -881,12 +881,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>OneEyedGregg</t>
+          <t>Fruity Slots (Josh/Jamie/Scottie)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -901,47 +901,47 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Kick ~14.9k (snippet)</t>
+          <t>78,700 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Kick https://kick.com/oneeyedgregg ; YouTube https://www.youtube.com/@Oneeyedgregg ; Twitch https://www.twitch.tv/oneeyedgregg ; X https://x.com/oneeyedgregg</t>
+          <t>YouTube @FruitySlots</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>none (oeg.gg hub)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>lacedupny (Laced Up Worldwide)</t>
+          <t>Rydurz</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>~20k IG ESTIMATE (pikdo mirror 2026-07-18)</t>
+          <t>12,801 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/lacedupny/</t>
+          <t>Kick https://kick.com/rydurz ; X https://x.com/rydurz</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>retail store (multi-location)</t>
+          <t>none (coderydurz.com hub)</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Rydurz</t>
+          <t>OneEyedGregg</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Kick ~24.2k (Sept-2025 snippet)</t>
+          <t>Kick ~14.9k (snippet)</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Kick https://kick.com/rydurz ; X https://x.com/rydurz</t>
+          <t>Kick https://kick.com/oneeyedgregg ; YouTube https://www.youtube.com/@Oneeyedgregg ; Twitch https://www.twitch.tv/oneeyedgregg ; X https://x.com/oneeyedgregg</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>none (coderydurz.com hub)</t>
+          <t>none (oeg.gg hub)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Jules (Julsy)</t>
+          <t>lacedupny (Laced Up Worldwide)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~20k IG ESTIMATE (pikdo mirror 2026-07-18)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/channel/UCrUFQtoCMdDZ06whZQodFuA ; X https://x.com/JulsyCS ; Kick https://kick.com/JULSY</t>
+          <t>Instagram https://www.instagram.com/lacedupny/</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>retail store (multi-location)</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>RobZn</t>
+          <t>Jules (Julsy)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Kick https://kick.com/robznnncs</t>
+          <t>YouTube https://www.youtube.com/channel/UCrUFQtoCMdDZ06whZQodFuA ; X https://x.com/JulsyCS ; Kick https://kick.com/JULSY</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>@the_happy_budget</t>
+          <t>RobZn</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_happy_budget</t>
+          <t>Kick https://kick.com/robznnncs</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>@winonakicks</t>
+          <t>@the_happy_budget</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@winonakicks</t>
+          <t>https://www.tiktok.com/@the_happy_budget</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Maria Ho</t>
+          <t>@winonakicks</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1475,22 +1475,22 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>mid-macro ESTIMATE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/maria_ho</t>
+          <t>https://www.tiktok.com/@winonakicks</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>https://www.mariaho.com</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -1500,32 +1500,32 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Little</t>
+          <t>Maria Ho</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>mid ESTIMATE</t>
+          <t>mid-macro ESTIMATE</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/jonathanlittlepoker ; site pokercoaching.com</t>
+          <t>IG https://instagram.com/maria_ho</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>https://pokercoaching.com</t>
+          <t>https://www.mariaho.com</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>mysterypacks.de</t>
+          <t>Jonathan Little</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1639,22 +1639,22 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>52.1k TikTok (2026-07-18)</t>
+          <t>mid ESTIMATE</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@mysterypacks.de</t>
+          <t>IG https://instagram.com/jonathanlittlepoker ; site pokercoaching.com</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>https://pokercoaching.com</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; reachable via site/store</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Svensk Drama</t>
+          <t>mysterypacks.de</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>~67.8k SUBS (2026-06-24, single-source)</t>
+          <t>52.1k TikTok (2026-07-18)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@SvenskDrama</t>
+          <t>TikTok https://www.tiktok.com/@mysterypacks.de</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>unboxdisneypinco</t>
+          <t>Svensk Drama</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>2,751 IG (2026-07-18)</t>
+          <t>~67.8k SUBS (2026-06-24, single-source)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/unboxdisneypinco/</t>
+          <t>YouTube https://www.youtube.com/@SvenskDrama</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>$50-300</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>$450-4,400</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CrimsonYT</t>
+          <t>GW1917</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>~5k YT SUBS (SERP)</t>
+          <t>453 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/channel/UCI2grI-9aZh9kyuPxWAFvxg ; X https://x.com/CrimsonYT101</t>
+          <t>YouTube https://www.youtube.com/@GW1917gaming</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (gw1917gaming.com)</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -1947,17 +1947,17 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Slot Squad</t>
+          <t>unboxdisneypinco</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>~16k IG</t>
+          <t>2,751 IG (2026-07-18)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/theslotsquad (16k)</t>
+          <t>Instagram https://www.instagram.com/unboxdisneypinco/</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1992,32 +1992,32 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2029,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>clvkingbets</t>
+          <t>Bouchonnoir</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2049,22 +2049,22 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>~18.8k</t>
+          <t>2,850 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>TikTok @clvkingbets (18.8k)</t>
+          <t>YouTube https://www.youtube.com/@Bouchonnoir</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (bouchonnoir.gg hub)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -2074,32 +2074,32 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -2111,17 +2111,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>gurusportsbetting</t>
+          <t>CrimsonYT</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>~19.3k</t>
+          <t>~5k YT SUBS (SERP)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>TikTok @gurusportsbetting (19.3k)</t>
+          <t>YouTube https://www.youtube.com/channel/UCI2grI-9aZh9kyuPxWAFvxg ; X https://x.com/CrimsonYT101</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -2156,22 +2156,22 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
@@ -2193,17 +2193,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>lucyburdge1</t>
+          <t>Sloth (SlothCSGO)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2213,22 +2213,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>~19.5k</t>
+          <t>5,880 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>TikTok @lucyburdge1 (19.5k)</t>
+          <t>YouTube https://www.youtube.com/@SlothCSGO ; X https://x.com/slothhcsgo</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (slothrewards.com hub)</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>brucie.sports</t>
+          <t>Aiden Gambles</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -2295,22 +2295,22 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>~23.9k</t>
+          <t>5,930 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>TikTok @brucie.sports (23.9k)</t>
+          <t>YouTube https://www.youtube.com/@AidenGambles ; X https://x.com/aiden_gambles</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (Discord community)</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
@@ -2320,32 +2320,32 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>codycoverspreads</t>
+          <t>Slot Squad</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2377,17 +2377,17 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>~27.2k</t>
+          <t>~16k IG</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>TikTok @codycoverspreads (27.2k)</t>
+          <t>IG https://instagram.com/theslotsquad (16k)</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2402,22 +2402,22 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>SweetFlips (group)</t>
+          <t>clvkingbets</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>~32k Kick</t>
+          <t>~18.8k</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Kick @SweetFlips (Dennylo, Damil, Jacko, Pingue, Baka, Motion, Blendz)</t>
+          <t>TikTok @clvkingbets (18.8k)</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Aiden Gambles</t>
+          <t>gurusportsbetting</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2541,22 +2541,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~19.3k</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@AidenGambles ; X https://x.com/aiden_gambles</t>
+          <t>TikTok @gurusportsbetting (19.3k)</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>none (Discord community)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2566,32 +2566,32 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bouchonnoir</t>
+          <t>lucyburdge1</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2623,22 +2623,22 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~19.5k</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@Bouchonnoir</t>
+          <t>TikTok @lucyburdge1 (19.5k)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>none (bouchonnoir.gg hub)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
@@ -2648,32 +2648,32 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>GW1917</t>
+          <t>brucie.sports</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2705,22 +2705,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~23.9k</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@GW1917gaming</t>
+          <t>TikTok @brucie.sports (23.9k)</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>none (gw1917gaming.com)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2730,32 +2730,32 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Sloth (SlothCSGO)</t>
+          <t>codycoverspreads</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -2787,22 +2787,22 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~27.2k</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@SlothCSGO ; X https://x.com/slothhcsgo</t>
+          <t>TikTok @codycoverspreads (27.2k)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>none (slothrewards.com hub)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -2812,32 +2812,32 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2849,17 +2849,17 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>TylerPlaysLive</t>
+          <t>SweetFlips (group)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>case-opening/mystery-box</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~32k Kick</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@tylerplayslive26 ; TikTok https://www.tiktok.com/@tylerplaylive ; X https://x.com/tylerplayslive ; Kick https://kick.com/tylerplayslive</t>
+          <t>Kick @SweetFlips (Dennylo, Damil, Jacko, Pingue, Baka, Motion, Blendz)</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>none (BlissBox LLC FB page)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2894,32 +2894,32 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>emilyyyrosess</t>
+          <t>TylerPlaysLive</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>nano-micro</t>
+          <t>micro-mid</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/emilyyyrosess/</t>
+          <t>YouTube https://www.youtube.com/@tylerplayslive26 ; TikTok https://www.tiktok.com/@tylerplaylive ; X https://x.com/tylerplayslive ; Kick https://kick.com/tylerplayslive</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (BlissBox LLC FB page)</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>golddigger_5</t>
+          <t>emilyyyrosess</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@golddigger_5</t>
+          <t>Instagram https://www.instagram.com/emilyyyrosess/</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>hypedropcrazybattles</t>
+          <t>golddigger_5</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@hypedropcrazybattles</t>
+          <t>TikTok https://www.tiktok.com/@golddigger_5</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Sebknowsbest</t>
+          <t>hypedropcrazybattles</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@sebknowsbest</t>
+          <t>TikTok https://www.tiktok.com/@hypedropcrazybattles</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>tshockz22</t>
+          <t>Sebknowsbest</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@tshockz22</t>
+          <t>TikTok https://www.tiktok.com/@sebknowsbest</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Brian Christopher (BCSlots)</t>
+          <t>tshockz22</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>nano-micro</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -3361,17 +3361,17 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>YouTube @BrianChristopherSlots ; site bcslots.com</t>
+          <t>TikTok https://www.tiktok.com/@tshockz22</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -3386,32 +3386,32 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); reachable via site/store</t>
+          <t>real-money case/box gambling - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>LetsGiveItASpin (Kim Hultman)</t>
+          <t>Brian Christopher (BCSlots)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>YouTube @LetsGiveItASpin</t>
+          <t>YouTube @BrianChristopherSlots ; site bcslots.com</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -3478,22 +3478,22 @@
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); reachable via site/store</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$6,000-30,000</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$90,000-700,000+</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CasinoGrounds</t>
+          <t>LetsGiveItASpin (Kim Hultman)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>mid-macro</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>YouTube (CasinoGrounds)</t>
+          <t>YouTube @LetsGiveItASpin</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -3669,17 +3669,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Fruity Slots (Josh/Jamie/Scottie)</t>
+          <t>BenderWins Sports Betting</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro ESTIMATE</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>YouTube @FruitySlots</t>
+          <t>TikTok @BenderWinsSportsBetting</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
     </row>
@@ -3751,12 +3751,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>BenderWins Sports Betting</t>
+          <t>Brett Stern</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>TikTok @BenderWinsSportsBetting</t>
+          <t>IG (gambling)</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -3796,22 +3796,22 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Brett Stern</t>
+          <t>weberbets</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>micro ESTIMATE</t>
+          <t>~40.4k</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>IG (gambling)</t>
+          <t>TikTok @weberbets (40.4k)</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>weberbets</t>
+          <t>Heart of Vegas Slots</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -3935,17 +3935,17 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>~40.4k</t>
+          <t>~47k IG</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>TikTok @weberbets (40.4k)</t>
+          <t>IG https://instagram.com/heartofvegasslots (47k)</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Heart of Vegas Slots</t>
+          <t>takingthepoints</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -4017,17 +4017,17 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>~47k IG</t>
+          <t>~60.4k</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/heartofvegasslots (47k)</t>
+          <t>TikTok @takingthepoints (60.4k)</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>takingthepoints</t>
+          <t>jommypogs</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>~60.4k</t>
+          <t>~61.4k TT</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>TikTok @takingthepoints (60.4k)</t>
+          <t>TikTok @jommypogs</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -4124,22 +4124,22 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>jommypogs</t>
+          <t>jstros_</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>~61.4k TT</t>
+          <t>~62.1k TT</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>TikTok @jommypogs</t>
+          <t>TikTok @jstros_</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>jstros_</t>
+          <t>binkyloveslots</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>TikTok @jstros_</t>
+          <t>TikTok @binkyloveslots</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>binkyloveslots</t>
+          <t>ahmed_elpoker</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>~62.1k TT</t>
+          <t>~62.3k TT</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>TikTok @binkyloveslots</t>
+          <t>TikTok @ahmed_elpoker</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>ahmed_elpoker</t>
+          <t>thadrunkgambler</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>~62.3k TT</t>
+          <t>~64k TT</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>TikTok @ahmed_elpoker</t>
+          <t>TikTok @thadrunkgambler</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>thadrunkgambler</t>
+          <t>thequeenofmedia</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>~64k TT</t>
+          <t>~79.8k TT</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>TikTok @thadrunkgambler</t>
+          <t>TikTok @thequeenofmedia</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>thequeenofmedia</t>
+          <t>erinkatedolan</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>sports-betting</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>~79.8k TT</t>
+          <t>~81.3k</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>TikTok @thequeenofmedia</t>
+          <t>TikTok @erinkatedolan (81.3k)</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -4616,14 +4616,14 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O49" s="6" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>erinkatedolan</t>
+          <t>Anthony Chico Reyes (Slot Machine Wins by Chico)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>sports-betting</t>
+          <t>gambling-casino</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -4673,17 +4673,17 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>~81.3k</t>
+          <t>~94k IG</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>TikTok @erinkatedolan (81.3k)</t>
+          <t>IG https://instagram.com/slotmachinewinsbychico (94k)</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -4698,22 +4698,22 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>sports-betting audience - core gambling fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Anthony Chico Reyes (Slot Machine Wins by Chico)</t>
+          <t>CasinoGrounds</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>~94k IG</t>
+          <t>130,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>IG https://instagram.com/slotmachinewinsbychico (94k)</t>
+          <t>YouTube (CasinoGrounds)</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -4790,22 +4790,22 @@
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; engaged micro/nano - sweet spot; contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
-          <t>$175-1,500</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>$4,400-27,000</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Cheesur</t>
+          <t>Dima_wallhacks</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -5657,17 +5657,17 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>~203k Kick ESTIMATE</t>
+          <t>203,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>https://kick.com/cheesur</t>
+          <t>https://www.youtube.com/@Dima_wallhacks</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>PimpCSGO (Jacob Winneche)</t>
+          <t>Cheesur</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -5739,17 +5739,17 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>~250k SUBS ESTIMATE</t>
+          <t>~203k Kick ESTIMATE</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@PIMP</t>
+          <t>https://kick.com/cheesur</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>ProdigyDDK</t>
+          <t>PimpCSGO (Jacob Winneche)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>~251-270k SUBS ESTIMATE (2026)</t>
+          <t>~250k SUBS ESTIMATE</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>YouTube https://www.youtube.com/@prodigyddk ; Instagram https://www.instagram.com/prodigy.ddk/ ; Twitch https://twitch.tv/prodigyddk</t>
+          <t>https://www.youtube.com/@PIMP</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>none (site prodigyddk.com)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Dima_wallhacks</t>
+          <t>ProdigyDDK</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>~406k SUBS ESTIMATE</t>
+          <t>258,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Dima_wallhacks</t>
+          <t>YouTube https://www.youtube.com/@prodigyddk ; Instagram https://www.instagram.com/prodigy.ddk/ ; Twitch https://twitch.tv/prodigyddk</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (site prodigyddk.com)</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Maherco</t>
+          <t>Orangie</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -5985,17 +5985,17 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>355,663 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>https://kick.com/maherco</t>
+          <t>Twitch https://www.twitch.tv/orangieyt ; Kick https://kick.com/orangie ; X https://x.com/orangie ; YouTube https://www.youtube.com/watch?v=o2pvnwCtc0U</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -6005,19 +6005,19 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
           <t>2</t>
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Renyan</t>
+          <t>Maherco</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>https://www.twitch.tv/renyan</t>
+          <t>https://kick.com/maherco</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Curly (The Curly Fella)</t>
+          <t>Renyan</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thecurlyfella</t>
+          <t>https://www.twitch.tv/renyan</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>@culturekicks</t>
+          <t>Curly (The Curly Fella)</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@culturekicks</t>
+          <t>https://www.tiktok.com/@thecurlyfella</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>@soleloco</t>
+          <t>@culturekicks</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soleloco</t>
+          <t>https://www.tiktok.com/@culturekicks</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>@air.jumps.official</t>
+          <t>@soleloco</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@air.jumps.official</t>
+          <t>https://www.tiktok.com/@soleloco</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>@ioannalaou</t>
+          <t>@air.jumps.official</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ioannalaou</t>
+          <t>https://www.tiktok.com/@air.jumps.official</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>csgo.gambling</t>
+          <t>@ioannalaou</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@csgo.gambling</t>
+          <t>https://www.tiktok.com/@ioannalaou</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>dizzydankss (DizzyDanks24)</t>
+          <t>csgo.gambling</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@dizzydankss</t>
+          <t>TikTok https://www.tiktok.com/@csgo.gambling</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>hypedropbalotelli</t>
+          <t>dizzydankss (DizzyDanks24)</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@hypedropbalotelli</t>
+          <t>TikTok https://www.tiktok.com/@dizzydankss</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>kelvinmboik</t>
+          <t>hypedropbalotelli</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@kelvinmboik</t>
+          <t>TikTok https://www.tiktok.com/@hypedropbalotelli</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>laceduphollywood</t>
+          <t>kelvinmboik</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -6892,17 +6892,17 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/laceduphollywood/</t>
+          <t>TikTok https://www.tiktok.com/@kelvinmboik</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>retail store</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>OnlyCrunchy</t>
+          <t>laceduphollywood</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>X https://x.com/onlycrunchy</t>
+          <t>Instagram https://www.instagram.com/laceduphollywood/</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>retail store</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>pizza_god1 (Kody Garrett)</t>
+          <t>OnlyCrunchy</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@pizza_god1</t>
+          <t>X https://x.com/onlycrunchy</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>quickhypedrop</t>
+          <t>pizza_god1 (Kody Garrett)</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@quickhypedrop</t>
+          <t>TikTok https://www.tiktok.com/@pizza_god1</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>rillabox.openings</t>
+          <t>quickhypedrop</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>TikTok https://www.tiktok.com/@rillabox.openings</t>
+          <t>TikTok https://www.tiktok.com/@quickhypedrop</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>twitch.tvkushti_ (kushti_)</t>
+          <t>rillabox.openings</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>Instagram https://www.instagram.com/twitch.tvkushti_/</t>
+          <t>TikTok https://www.tiktok.com/@rillabox.openings</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>@harrisonevel</t>
+          <t>twitch.tvkushti_ (kushti_)</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -7387,7 +7387,11 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Instagram https://www.instagram.com/twitch.tvkushti_/</t>
+        </is>
+      </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
           <t>none</t>
@@ -7437,7 +7441,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>@yankeekicks</t>
+          <t>@harrisonevel</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -7462,7 +7466,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Instagram/YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr"/>
@@ -7515,7 +7519,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>ArrowCS</t>
+          <t>@yankeekicks</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -7540,7 +7544,7 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Instagram/YouTube</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr"/>
@@ -7593,7 +7597,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Devon Gard</t>
+          <t>ArrowCS</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -7618,7 +7622,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>YouTube/LinkedIn</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr"/>
@@ -7671,7 +7675,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>megalodon888</t>
+          <t>Devon Gard</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -7696,7 +7700,7 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Twitch/Kick</t>
+          <t>YouTube/LinkedIn</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
@@ -7749,17 +7753,17 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Raja Richter (The Big Jackpot)</t>
+          <t>megalodon888</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>gambling-casino</t>
+          <t>case-opening/mystery-box</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -7769,19 +7773,15 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>YouTube @TheBigJackpot ; IG @thebigjackpot</t>
-        </is>
-      </c>
+          <t>Twitch/Kick</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="4" t="inlineStr">
         <is>
           <t>none</t>
@@ -7794,32 +7794,32 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money case/box gambling - core gambling fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>N/A ESTIMATE</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Lady Luck HQ</t>
+          <t>Pompsie Slots</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>YouTube @LadyLuckHQ</t>
+          <t>YouTube (Pompsie)</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -7886,22 +7886,22 @@
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>NG Slot</t>
+          <t>PokerMetarb</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>YouTube @NGSlot</t>
+          <t>YouTube (PokerMetarb)</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -7968,22 +7968,22 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N90" s="5" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Mr. Hand Pay</t>
+          <t>CasinoDaddy</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>YouTube @MrHandPay</t>
+          <t>Twitch https://twitch.tv/casinodaddy</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Pompsie Slots</t>
+          <t>Taour (Noamane Boukhari)</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -8097,17 +8097,17 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>mid-macro</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>YouTube (Pompsie)</t>
+          <t>Kick (Taour)</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>PokerMetarb</t>
+          <t>Tiagovski</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>YouTube (PokerMetarb)</t>
+          <t>Kick/Twitch @Tiagovski555</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CasinoDaddy</t>
+          <t>teufeurs</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>Twitch https://twitch.tv/casinodaddy</t>
+          <t>Twitch @teufeurs</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -8296,22 +8296,22 @@
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
         <is>
-          <t>real-money gambling/casino audience - TOP GemBreak fit; macro reach (higher cost); contact needs enrichment</t>
+          <t>real-money gambling/casino audience - TOP GemBreak fit; contact needs enrichment</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Taour (Noamane Boukhari)</t>
+          <t>YoutubeVLR</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -8343,17 +8343,17 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Kick (Taour)</t>
+          <t>YouTube (VLR)</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Tiagovski</t>
+          <t>All Casino Action</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>Kick/Twitch @Tiagovski555</t>
+          <t>YouTube (All Casino Action)</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>teufeurs</t>
+          <t>Chipmonkz Slots</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Twitch @teufeurs</t>
+          <t>YouTube (Chipmonkz)</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>YoutubeVLR</t>
+          <t>Toaster (Toaster Gambles)</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>YouTube (VLR)</t>
+          <t>YouTube/Kick (Toaster)</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>All Casino Action</t>
+          <t>Cabrzy</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>YouTube (All Casino Action)</t>
+          <t>YouTube/Kick (Cabrzy)</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chipmonkz Slots</t>
+          <t>TactPlaysGames</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>YouTube (Chipmonkz)</t>
+          <t>YouTube (Tact)</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Toaster (Toaster Gambles)</t>
+          <t>The Bandit (NightRush/Slot Video)</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>YouTube/Kick (Toaster)</t>
+          <t>YouTube (The Bandit)</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>60,625 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9081,17 +9081,17 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>modash/WSJ coverage</t>
+          <t>modash/WSJ coverage +LunarCrush</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>680,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>~1M+ ESTIMATE</t>
+          <t>1,610,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>1,200,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>1,260,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>1,140,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>130,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>318,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>78,700 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr"/>
@@ -12381,17 +12381,17 @@
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr"/>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="O91" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P91" s="6" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="O93" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P93" s="6" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O95" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P95" s="6" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="O105" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P105" s="6" t="inlineStr">
@@ -22475,7 +22475,7 @@
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>~1.74M YT / 419k IG</t>
+          <t>2,060,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="O169" s="6" t="inlineStr">
         <is>
-          <t>favikon/feedspot/press</t>
+          <t>favikon/feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P169" s="6" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>~600k+ YT</t>
+          <t>1,490,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -22605,7 +22605,7 @@
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>favikon/feedspot/press</t>
+          <t>favikon/feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>~300-600k YT</t>
+          <t>599,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="O171" s="6" t="inlineStr">
         <is>
-          <t>favikon/feedspot/press</t>
+          <t>favikon/feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P171" s="6" t="inlineStr">
@@ -23623,7 +23623,7 @@
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>~334k</t>
+          <t>~334k YT ESTIMATE</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>macro ESTIMATE</t>
+          <t>1,170,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -24569,7 +24569,7 @@
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>press +LunarCrush</t>
         </is>
       </c>
       <c r="P194" s="4" t="inlineStr">
@@ -25175,7 +25175,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>macro &gt;&gt;1M</t>
+          <t>1,004,182 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>macro (multi-M)</t>
+          <t>675,558 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -25679,12 +25679,12 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>~553k SUBS ESTIMATE</t>
+          <t>549,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr"/>
@@ -25763,12 +25763,12 @@
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>N/A (crowded namespace)</t>
+          <t>355,663 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G209" s="6" t="inlineStr"/>
@@ -25814,12 +25814,12 @@
       </c>
       <c r="P209" s="6" t="inlineStr">
         <is>
-          <t>$6,000-30,000</t>
+          <t>$1,500-6,000</t>
         </is>
       </c>
       <c r="Q209" s="6" t="inlineStr">
         <is>
-          <t>$90,000-700,000+</t>
+          <t>$27,000-90,000</t>
         </is>
       </c>
       <c r="R209" s="7" t="inlineStr"/>
@@ -25847,12 +25847,12 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>~535-559k SUBS ESTIMATE (2026)</t>
+          <t>573,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr"/>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>~535k SUBS ESTIMATE</t>
+          <t>538,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G211" s="6" t="inlineStr"/>
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>~526k SUBS ESTIMATE</t>
+          <t>529,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="G213" s="6" t="inlineStr"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>~406k SUBS ESTIMATE</t>
+          <t>203,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
@@ -26267,7 +26267,7 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>~251-270k SUBS ESTIMATE (2026)</t>
+          <t>258,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F215" s="6" t="inlineStr">
@@ -26855,12 +26855,12 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5,930 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr"/>
@@ -26906,12 +26906,12 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="Q222" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
       <c r="R222" s="5" t="inlineStr"/>
@@ -26939,12 +26939,12 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2,850 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="G223" s="6" t="inlineStr"/>
@@ -26990,12 +26990,12 @@
       </c>
       <c r="P223" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="Q223" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
       <c r="R223" s="7" t="inlineStr"/>
@@ -27023,12 +27023,12 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>453 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr"/>
@@ -27074,12 +27074,12 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="Q224" s="4" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
       <c r="R224" s="5" t="inlineStr"/>
@@ -27107,12 +27107,12 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5,880 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>micro-mid</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="G225" s="6" t="inlineStr"/>
@@ -27158,12 +27158,12 @@
       </c>
       <c r="P225" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$50-300</t>
         </is>
       </c>
       <c r="Q225" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$450-4,400</t>
         </is>
       </c>
       <c r="R225" s="7" t="inlineStr"/>
@@ -27779,7 +27779,7 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>Kick ~24.2k (Sept-2025 snippet)</t>
+          <t>12,801 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F233" s="6" t="inlineStr">
@@ -30574,12 +30574,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>60,625 X (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -30616,17 +30616,17 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>modash/WSJ coverage</t>
+          <t>modash/WSJ coverage +LunarCrush</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>N/A ESTIMATE</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
@@ -31550,7 +31550,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>680,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -31592,7 +31592,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>~1M+ ESTIMATE</t>
+          <t>1,610,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -31672,7 +31672,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
@@ -31710,7 +31710,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>1,200,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -31870,7 +31870,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>1,260,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -31912,7 +31912,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -32030,7 +32030,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>1,140,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -32072,7 +32072,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -33394,7 +33394,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>130,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -33634,7 +33634,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>mid-macro</t>
+          <t>318,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -33676,7 +33676,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -33874,12 +33874,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>78,700 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr"/>
@@ -33916,17 +33916,17 @@
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>StreamRollers/Feedspot/press</t>
+          <t>StreamRollers/Feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>$1,500-6,000</t>
+          <t>$175-1,500</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>$27,000-90,000</t>
+          <t>$4,400-27,000</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr"/>
@@ -37861,7 +37861,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>~1.74M YT / 419k IG</t>
+          <t>2,060,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -37907,7 +37907,7 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>favikon/feedspot/press</t>
+          <t>favikon/feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
@@ -37945,7 +37945,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>~600k+ YT</t>
+          <t>1,490,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -37991,7 +37991,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>favikon/feedspot/press</t>
+          <t>favikon/feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
@@ -38029,7 +38029,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>~300-600k YT</t>
+          <t>599,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -38071,7 +38071,7 @@
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>favikon/feedspot/press</t>
+          <t>favikon/feedspot/press +LunarCrush</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
@@ -39009,7 +39009,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>~334k</t>
+          <t>~334k YT ESTIMATE</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -39909,7 +39909,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>macro ESTIMATE</t>
+          <t>1,170,000 YT (LunarCrush 2026-07-19)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>press +LunarCrush</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -40646,7 +40646,7 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
@@ -40726,7 +40726,7 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
@@ -40806,7 +40806,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
@@ -40886,7 +40886,7 @@
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
@@ -40966,7 +40966,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -41050,7 +41050,7 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
@@ -41858,7 +41858,7 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>feedspot/socialveins/press</t>
+          <t>feedspot/socialveins/press +LunarCrush</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
